--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1421,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1488,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1524,911 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1851,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1961,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1976,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2076,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2091,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,13 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2423,12 +2479,817 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1832,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1941,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2018,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2056,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2133,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2171,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2204,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2228,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2282,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2315,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,37 +2359,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2430,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,37 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2512,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2545,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2944,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3059,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3182,22 +3210,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3230,12 +3258,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3249,47 +3277,852 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>09:18</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>10/11</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2770,32 +2770,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,37 +2831,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2885,32 +2889,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -2918,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2942,17 +2950,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2962,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3000,32 +3008,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3033,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,17 +3069,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3077,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3115,32 +3127,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3148,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3172,17 +3188,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3192,12 +3208,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3230,32 +3246,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3263,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,37 +3307,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3345,32 +3365,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3378,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,37 +3426,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3460,32 +3484,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3493,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3545,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3537,17 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3575,32 +3603,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3608,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3632,37 +3664,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3953,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4144,592 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
           <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,14 +3203,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>70.7</t>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,14 +3560,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3613,24 +3613,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3722,32 +3722,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3779,17 +3783,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3799,7 +3803,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3837,32 +3841,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -3870,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3902,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3914,7 +3922,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3952,32 +3960,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3985,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4021,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4029,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4079,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4100,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,37 +4140,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4182,32 +4198,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4215,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4259,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4259,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4384,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4494,12 +4514,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4739,477 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>11/11</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>70.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>73.3</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>70.5</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,14 +3084,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>73.3</t>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,14 +4036,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>73.3</t>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4208,24 +4208,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4317,32 +4317,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4378,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4394,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4436,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4465,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4497,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4509,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4547,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4580,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,37 +4616,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4662,32 +4674,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4695,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4735,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,12 +4755,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4925,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4974,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5199,17 +5215,477 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>2/11</t>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,17 +2612,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4684,24 +4684,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,17 +4750,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4793,32 +4793,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4850,17 +4854,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4870,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4908,32 +4912,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4941,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4973,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4985,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5031,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5056,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,37 +5092,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5138,32 +5150,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5171,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5631,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,17 +5691,477 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>70.7</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>4/11</t>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5041,24 +5041,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5160,24 +5160,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5269,32 +5269,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5330,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5346,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5384,32 +5388,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5417,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,37 +5449,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5499,32 +5507,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5532,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5556,37 +5568,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5614,32 +5626,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5647,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5691,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5877,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6107,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6167,477 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
-        <is>
-          <t>73.3</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>10/11</t>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>69.7</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5279,24 +5279,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,22 +3560,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5745,32 +5745,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5806,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5822,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5864,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5893,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,37 +5925,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6008,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,27 +6044,27 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6090,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6123,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6163,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6238,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,32 +6282,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6583,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6647,592 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>72.8</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>8/11</t>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>72.6</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3203,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5993,12 +5993,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6340,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,37 +6401,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6455,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,37 +6520,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6570,32 +6578,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6603,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6639,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6697,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6718,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,37 +6758,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6898,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6948,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6987,7 +7003,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7063,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,6 +7252,696 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,17 +3560,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,17 +5107,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,17 +5940,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,12 +6059,12 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6588,19 +6588,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6707,24 +6707,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6816,32 +6816,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,27 +6877,27 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6931,32 +6935,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6964,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6996,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7008,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7046,32 +7054,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7079,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7103,32 +7115,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7161,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7194,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7238,12 +7254,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7276,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7309,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,37 +7353,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7463,7 +7483,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7539,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7654,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7818,12 +7838,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,17 +7948,707 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>68.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>69.2</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>1/11</t>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,17 +3084,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,22 +3441,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,22 +4393,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,17 +5345,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,17 +6178,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,22 +6535,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7526,32 +7526,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7559,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,37 +7587,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7645,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7674,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,32 +7706,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7756,32 +7764,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7789,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7825,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,12 +7845,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7871,32 +7883,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7904,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,37 +7944,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7986,32 +8002,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8019,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,37 +8063,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8308,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8303,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8423,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8479,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8594,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8652,6 +8672,696 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,17 +2965,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,17 +4155,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,17 +4988,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,17 +7602,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7726,17 +7726,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7905,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8002,36 +8002,32 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8039,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8059,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8117,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8236,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8351,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8384,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8428,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8466,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8499,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,32 +8535,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8581,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8614,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,37 +8654,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -8696,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8729,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8753,17 +8773,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8773,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -8811,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8844,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,32 +8892,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8959,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9027,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9113,7 +9137,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9189,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,12 +9257,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9304,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9372,477 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>10/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8079,17 +8079,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8950,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8983,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9011,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9027,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9065,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9098,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9130,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9142,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9213,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9367,7 +9375,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9443,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9558,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9612,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9788,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,17 +9840,132 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
           <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC80"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8960,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9188,32 +9188,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9221,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,17 +9249,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9265,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9303,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9336,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,17 +9368,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9380,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9418,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9451,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9487,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9495,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9605,7 +9617,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9620,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9735,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9862,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,17 +9967,132 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-25-182路.xlsx
+++ b/data/export/2026-09-25-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,17 +9150,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9436,24 +9436,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9545,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9578,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9606,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9622,17 +9626,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -9660,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9693,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9725,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9737,17 +9745,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9783,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9808,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,17 +9844,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9852,17 +9864,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10038,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,17 +10094,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
